--- a/1-LATEX/2-DADOS/3-OUTPUT/resultados_por_dimensao.xlsx
+++ b/1-LATEX/2-DADOS/3-OUTPUT/resultados_por_dimensao.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P7"/>
+  <dimension ref="A1:P9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -500,34 +500,34 @@
         <v>37</v>
       </c>
       <c r="C3">
-        <v>0.04486936865596249</v>
+        <v>0.01655094282820235</v>
       </c>
       <c r="D3">
-        <v>0.0506784021094261</v>
+        <v>0.04715143097179037</v>
       </c>
       <c r="E3">
-        <v>-0.06699133405655323</v>
+        <v>-0.08578097560573668</v>
       </c>
       <c r="F3">
-        <v>0.1567300713684782</v>
+        <v>0.1188828612621414</v>
       </c>
       <c r="G3">
-        <v>-0.2573821296825256</v>
+        <v>-0.300246458848912</v>
       </c>
       <c r="H3">
-        <v>0.3471208669944505</v>
+        <v>0.3333483445053167</v>
       </c>
       <c r="I3">
-        <v>0.02121684598240538</v>
+        <v>0.02389601709455585</v>
       </c>
       <c r="J3">
-        <v>2.438881119934042</v>
+        <v>3.642037642435129</v>
       </c>
       <c r="K3">
-        <v>71.56436801653555</v>
+        <v>253.3945509577271</v>
       </c>
       <c r="L3">
-        <v>0.0003834809409339813</v>
+        <v>9.428090080173074E-22</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -535,13 +535,13 @@
         </is>
       </c>
       <c r="N3">
-        <v>4.589122480808405</v>
+        <v>1.668866846300987</v>
       </c>
       <c r="O3">
-        <v>-6.479669427938095</v>
+        <v>-8.220477124829873</v>
       </c>
       <c r="P3">
-        <v>16.96798412059299</v>
+        <v>12.62379844651944</v>
       </c>
     </row>
     <row r="4">
@@ -554,34 +554,34 @@
         <v>37</v>
       </c>
       <c r="C4">
-        <v>0.0715762333288117</v>
+        <v>0.007406689765167936</v>
       </c>
       <c r="D4">
-        <v>0.07407978426245312</v>
+        <v>0.1024738071770136</v>
       </c>
       <c r="E4">
-        <v>-0.08972584688411218</v>
+        <v>-0.2098302317032646</v>
       </c>
       <c r="F4">
-        <v>0.2328783135417356</v>
+        <v>0.2246436112336005</v>
       </c>
       <c r="G4">
-        <v>-0.2849219258300118</v>
+        <v>-0.621592444058011</v>
       </c>
       <c r="H4">
-        <v>0.4280743924876352</v>
+        <v>0.6364058235883467</v>
       </c>
       <c r="I4">
-        <v>0.02766083366641499</v>
+        <v>0.09260327465062979</v>
       </c>
       <c r="J4">
-        <v>6.074724194413331</v>
+        <v>7.629654219477611</v>
       </c>
       <c r="K4">
-        <v>26.26739414566603</v>
+        <v>37.43656165331914</v>
       </c>
       <c r="L4">
-        <v>0.8829643996734777</v>
+        <v>0.4030297403812925</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -589,13 +589,13 @@
         </is>
       </c>
       <c r="N4">
-        <v>7.420003742468806</v>
+        <v>0.7434187138053883</v>
       </c>
       <c r="O4">
-        <v>-8.58182232979814</v>
+        <v>-18.92781308413174</v>
       </c>
       <c r="P4">
-        <v>26.22278739421007</v>
+        <v>25.18764819650625</v>
       </c>
     </row>
     <row r="5">
@@ -608,34 +608,34 @@
         <v>37</v>
       </c>
       <c r="C5">
-        <v>0.007406689765167936</v>
+        <v>-0.2787297834861159</v>
       </c>
       <c r="D5">
-        <v>0.1024738071770136</v>
+        <v>0.1053211656444903</v>
       </c>
       <c r="E5">
-        <v>-0.2098302317032646</v>
+        <v>-0.494023149580271</v>
       </c>
       <c r="F5">
-        <v>0.2246436112336005</v>
+        <v>-0.06343641739196074</v>
       </c>
       <c r="G5">
-        <v>-0.621592444058011</v>
+        <v>-1.113866715737241</v>
       </c>
       <c r="H5">
-        <v>0.6364058235883467</v>
+        <v>0.5564071487650096</v>
       </c>
       <c r="I5">
-        <v>0.09260327465062979</v>
+        <v>0.1706084965332423</v>
       </c>
       <c r="J5">
-        <v>7.629654219477611</v>
+        <v>30.68844264259262</v>
       </c>
       <c r="K5">
-        <v>37.43656165331914</v>
+        <v>125.9213409842246</v>
       </c>
       <c r="L5">
-        <v>0.4030297403812925</v>
+        <v>6.653162462603422E-12</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -643,13 +643,13 @@
         </is>
       </c>
       <c r="N5">
-        <v>0.7434187138053883</v>
+        <v>-24.32556395870801</v>
       </c>
       <c r="O5">
-        <v>-18.92781308413174</v>
+        <v>-38.98333421748406</v>
       </c>
       <c r="P5">
-        <v>25.18764819650625</v>
+        <v>-6.14662081702061</v>
       </c>
     </row>
     <row r="6">
@@ -662,34 +662,34 @@
         <v>37</v>
       </c>
       <c r="C6">
-        <v>-0.2787297834861159</v>
+        <v>0.1716000516464709</v>
       </c>
       <c r="D6">
-        <v>0.1053211656444903</v>
+        <v>0.1058399698656821</v>
       </c>
       <c r="E6">
-        <v>-0.494023149580271</v>
+        <v>-0.05482597277927126</v>
       </c>
       <c r="F6">
-        <v>-0.06343641739196074</v>
+        <v>0.398026076072213</v>
       </c>
       <c r="G6">
-        <v>-1.113866715737241</v>
+        <v>-0.4852238459279455</v>
       </c>
       <c r="H6">
-        <v>0.5564071487650096</v>
+        <v>0.8284239492208872</v>
       </c>
       <c r="I6">
-        <v>0.1706084965332423</v>
+        <v>0.101150822222562</v>
       </c>
       <c r="J6">
-        <v>30.68844264259262</v>
+        <v>8.40253021833796</v>
       </c>
       <c r="K6">
-        <v>125.9213409842246</v>
+        <v>46.24359044734756</v>
       </c>
       <c r="L6">
-        <v>6.653162462603422E-12</v>
+        <v>0.1178926285696138</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -697,13 +697,13 @@
         </is>
       </c>
       <c r="N6">
-        <v>-24.32556395870801</v>
+        <v>18.7202918397019</v>
       </c>
       <c r="O6">
-        <v>-38.98333421748406</v>
+        <v>-5.335012353354984</v>
       </c>
       <c r="P6">
-        <v>-6.14662081702061</v>
+        <v>48.8882853617898</v>
       </c>
     </row>
     <row r="7">
@@ -713,37 +713,37 @@
         </is>
       </c>
       <c r="B7">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="C7">
-        <v>0.1716000516464709</v>
+        <v>0</v>
       </c>
       <c r="D7">
-        <v>0.1058399698656821</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>-0.05482597277927126</v>
+        <v>0</v>
       </c>
       <c r="F7">
-        <v>0.398026076072213</v>
+        <v>0</v>
       </c>
       <c r="G7">
-        <v>-0.4852238459279455</v>
+        <v>-0.7100502051691578</v>
       </c>
       <c r="H7">
-        <v>0.8284239492208872</v>
+        <v>0.7100502051691578</v>
       </c>
       <c r="I7">
-        <v>0.101150822222562</v>
+        <v>2.991635273407584E-09</v>
       </c>
       <c r="J7">
-        <v>8.40253021833796</v>
+        <v>4.849856232471125E-08</v>
       </c>
       <c r="K7">
-        <v>46.24359044734756</v>
+        <v>0</v>
       </c>
       <c r="L7">
-        <v>0.1178926285696138</v>
+        <v>1</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -751,13 +751,121 @@
         </is>
       </c>
       <c r="N7">
-        <v>18.7202918397019</v>
+        <v>0</v>
       </c>
       <c r="O7">
-        <v>-5.335012353354984</v>
+        <v>0</v>
       </c>
       <c r="P7">
-        <v>48.8882853617898</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>V7</t>
+        </is>
+      </c>
+      <c r="B8">
+        <v>47</v>
+      </c>
+      <c r="C8">
+        <v>0.05120757691971459</v>
+      </c>
+      <c r="D8">
+        <v>0.0286313327549371</v>
+      </c>
+      <c r="E8">
+        <v>-0.008771158994193784</v>
+      </c>
+      <c r="F8">
+        <v>0.111186312833623</v>
+      </c>
+      <c r="G8">
+        <v>-0.5596308859052627</v>
+      </c>
+      <c r="H8">
+        <v>0.6620460397446918</v>
+      </c>
+      <c r="I8">
+        <v>2.050008407799427E-09</v>
+      </c>
+      <c r="J8">
+        <v>3.484765520565583E-08</v>
+      </c>
+      <c r="K8">
+        <v>0.06912388442620486</v>
+      </c>
+      <c r="L8">
+        <v>1</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Confirmatória (meta-análise completa)</t>
+        </is>
+      </c>
+      <c r="N8">
+        <v>5.254135390084347</v>
+      </c>
+      <c r="O8">
+        <v>-0.8732804598560517</v>
+      </c>
+      <c r="P8">
+        <v>11.76031112608042</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>V8</t>
+        </is>
+      </c>
+      <c r="B9">
+        <v>47</v>
+      </c>
+      <c r="C9">
+        <v>0.2796759127099698</v>
+      </c>
+      <c r="D9">
+        <v>0.06830923323932046</v>
+      </c>
+      <c r="E9">
+        <v>0.03385813407672725</v>
+      </c>
+      <c r="F9">
+        <v>0.5254936913432123</v>
+      </c>
+      <c r="G9">
+        <v>0.04126572789340124</v>
+      </c>
+      <c r="H9">
+        <v>0.5180860975265383</v>
+      </c>
+      <c r="I9">
+        <v>4.655057934973063E-10</v>
+      </c>
+      <c r="J9">
+        <v>9.09172822407833E-09</v>
+      </c>
+      <c r="K9">
+        <v>2.306511664550499</v>
+      </c>
+      <c r="L9">
+        <v>1</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Confirmatória (meta-análise completa)</t>
+        </is>
+      </c>
+      <c r="N9">
+        <v>32.27010722605556</v>
+      </c>
+      <c r="O9">
+        <v>3.443784483818235</v>
+      </c>
+      <c r="P9">
+        <v>69.12936193212317</v>
       </c>
     </row>
   </sheetData>
